--- a/data/externalStats/File1/RPT_RPT8077949212208QB_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT8077949212208QB_externalStats.xlsx
@@ -2140,7 +2140,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454168</v>
+        <v>96.12539893454166</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>BREZTRI AEROSPHERE</t>
+          <t>HUMIRA PEN</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>3756859.621717962</v>
+        <v>846073.338045736</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>1210.913003344472</v>
+        <v>189.4409895539809</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -2246,19 +2246,19 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>GEMTESA</t>
+          <t>DUPIXENT</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>2402554.099908541</v>
+        <v>707223.1856686914</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>682.8589505041771</v>
+        <v>580.7009912939548</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -2294,7 +2294,7 @@
         <v>2178510</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>56.5609310394383</v>
+        <v>56.56093103943829</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>44.72499948674783</v>
@@ -2323,19 +2323,19 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>CREON</t>
+          <t>BREZTRI AEROSPHERE</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1144686.286052053</v>
+        <v>684422.7708849865</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>183.2779633371303</v>
+        <v>1210.913003344472</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -2400,19 +2400,19 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>STIOLTO RESPIMAT</t>
+          <t>SKYRIZI PEN</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>945150.4060012742</v>
+        <v>562819.203762886</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>389.2615316687251</v>
+        <v>67.70495355457277</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -2448,7 +2448,7 @@
         <v>2277007</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>55.339626796155</v>
+        <v>55.33962679615498</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>45.12946189673967</v>
@@ -2477,19 +2477,19 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>HUMIRA PEN</t>
+          <t>TRULICITY</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>846073.338045736</v>
+        <v>510027.4491912912</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>189.4409895539809</v>
+        <v>758.1776779944732</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -2540,19 +2540,19 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>DUPIXENT</t>
+          <t>GEMTESA</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>707223.1856686914</v>
+        <v>429443.7322096582</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>580.7009912939548</v>
+        <v>682.8589505041771</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -2611,19 +2611,19 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>SPIRIVA RESPIMAT</t>
+          <t>SKYRIZI</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>701360.6185720146</v>
+        <v>369106.5344350918</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>326.6424257603529</v>
+        <v>45.78173533647929</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -2688,19 +2688,19 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>ZENPEP</t>
+          <t>ERLEADA</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>689799.1542632086</v>
+        <v>331091.2838799802</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>41.55721261714001</v>
+        <v>71.14983151653553</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -2765,19 +2765,19 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>PAXLOVID</t>
+          <t>RINVOQ</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>MISC. ANTIVIRALS</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>665303.6848965359</v>
+        <v>242906.6009746044</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>397.3074031341286</v>
+        <v>80.22009841522772</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -2842,19 +2842,19 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>SKYRIZI PEN</t>
+          <t>CREON</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>562819.203762886</v>
+        <v>210371.4937818139</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>67.70495355457277</v>
+        <v>183.2779633371303</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -2919,19 +2919,19 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>TRULICITY</t>
+          <t>COSENTYX UNOREADY</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>510027.4491912912</v>
+        <v>196882.514267751</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>758.1776779944734</v>
+        <v>42.53972034371863</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -2996,19 +2996,19 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>MULTAQ</t>
+          <t>STIOLTO RESPIMAT</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>ANTIARRHYTHMICS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>405978.3514136001</v>
+        <v>172281.352010263</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>108.1413547605109</v>
+        <v>389.2615316687251</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -3073,19 +3073,19 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>XTAMPZA ER</t>
+          <t>COSENTYX SENSOREADY PEN</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>OPIOID AGONISTS &amp; COMBOS</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>400612.4933541995</v>
+        <v>145976.1620390519</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>182.4815355620256</v>
+        <v>36.41682867681511</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="AN38" s="58" t="n">
-        <v>649.121129802971</v>
+        <v>649.1211298029712</v>
       </c>
     </row>
     <row r="39">
@@ -3136,19 +3136,19 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>BELSOMRA</t>
+          <t>FREESTYLE LIBRE 3 PLUS/SENSOR/GLUCOSE MONITORING SYSTEM</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>SEDATIVE HYPNOTICS</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>400544.4827065276</v>
+        <v>128970.4516744092</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>178.1609603833926</v>
+        <v>1776.792378096958</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -3203,19 +3203,19 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>ROCKLATAN</t>
+          <t>SPIRIVA RESPIMAT</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>379419.1592751544</v>
+        <v>127944.8341090888</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>186.9728449784303</v>
+        <v>326.6424257603529</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -3280,19 +3280,19 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>SKYRIZI</t>
+          <t>ZENPEP</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>369059.4895921383</v>
+        <v>125277.0213423983</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>45.78173533647929</v>
+        <v>41.55721261714001</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>75.69141383091859</v>
+        <v>75.69141383091858</v>
       </c>
     </row>
     <row r="42">
@@ -3357,19 +3357,19 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>ERLEADA</t>
+          <t>PAXLOVID</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>MISC. ANTIVIRALS</t>
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>331091.2838799802</v>
+        <v>123126.7710396887</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>71.14983151653553</v>
+        <v>397.3074031341286</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -3434,19 +3434,19 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>LOKELMA</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>POTASSIUM REMOVING AGENTS</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>279872.4569388183</v>
+        <v>89076.01605878503</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>94.93499361844026</v>
+        <v>238.3357959989694</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -3511,19 +3511,19 @@
       </c>
       <c r="AF44" s="82" t="inlineStr">
         <is>
-          <t>XIIDRA</t>
+          <t>EMGALITY</t>
         </is>
       </c>
       <c r="AG44" s="82" t="inlineStr">
         <is>
-          <t>OPHTHALMIC INTEGRIN ANTAGONIST</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>268732.7076555117</v>
+        <v>85657.95523092154</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>49.17758916476652</v>
+        <v>204.0127137102595</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -3553,7 +3553,7 @@
         <v>2038</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>72790.87999999999</v>
+        <v>72790.88</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>108490</v>
@@ -3706,14 +3706,14 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>4798347.609120487</v>
+        <v>2605725.704537616</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>1746.424073544983</v>
+        <v>612.6259182172483</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -3752,14 +3752,14 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>2605678.659694662</v>
+        <v>874429.2554824201</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>612.6259182172483</v>
+        <v>1746.424073544983</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -3873,14 +3873,14 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>2402554.099908541</v>
+        <v>707223.1856686914</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>683.223513430522</v>
+        <v>586.0125314758862</v>
       </c>
     </row>
     <row r="53">
@@ -3908,7 +3908,7 @@
         <v>1360.461874663778</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>1442.583703144494</v>
+        <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>16.81060051458184</v>
@@ -3917,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="129" t="n">
-        <v>2819.856178322854</v>
+        <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
         <v>1374.950469289653</v>
@@ -3947,21 +3947,21 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>2899.923685528718</v>
+        <v>2899.923685528717</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>1834485.440315262</v>
+        <v>429443.7322096583</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>224.8351759542703</v>
+        <v>683.223513430522</v>
       </c>
     </row>
     <row r="54">
@@ -4035,14 +4035,14 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>936588.5137576791</v>
+        <v>335648.5151242121</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>462.5086911719521</v>
+        <v>224.8351759542703</v>
       </c>
     </row>
     <row r="55">
@@ -4070,7 +4070,7 @@
         <v>9604.744793221946</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>7.468734608523377</v>
+        <v>7.468734608523375</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>0</v>
@@ -4082,10 +4082,10 @@
         <v>9612.213527830469</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>9711.100612668351</v>
+        <v>9711.100612668355</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -4094,10 +4094,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>9718.782032960185</v>
+        <v>9718.782032960189</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473897</v>
+        <v>9788.465905473899</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>7.841870691875751</v>
@@ -4109,21 +4109,21 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165773</v>
+        <v>9796.307776165775</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>MISC. ANTIVIRALS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>793934.5434224507</v>
+        <v>331091.2838799803</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>473.1751484562236</v>
+        <v>112.8666877814321</v>
       </c>
     </row>
     <row r="56">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>707223.1856686914</v>
+        <v>235550.3646270174</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>586.0125314758862</v>
+        <v>457.5545255467091</v>
       </c>
     </row>
     <row r="57">
@@ -4241,7 +4241,7 @@
         <v>41.96486816008204</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>2850.466064366342</v>
+        <v>2850.466064366343</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>1635.212972539078</v>
@@ -4262,7 +4262,7 @@
         <v>1409.614172356645</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>964.2203879681115</v>
+        <v>964.2203879681116</v>
       </c>
       <c r="X57" s="131" t="n">
         <v>9.804214882119291</v>
@@ -4278,14 +4278,14 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>542395.169130032</v>
+        <v>179096.9157866754</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>272.1384864083959</v>
+        <v>462.5086911719521</v>
       </c>
     </row>
     <row r="58">
@@ -4359,14 +4359,14 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>POTASSIUM REMOVING AGENTS</t>
+          <t>BASAL INSULIN</t>
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>415878.6061316487</v>
+        <v>164356.4629033951</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>130.8563425551474</v>
+        <v>1638.122906921952</v>
       </c>
     </row>
     <row r="59">
@@ -4430,24 +4430,24 @@
         <v>0</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>1395.880080084952</v>
+        <v>1395.880080084951</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>1395.880080084952</v>
+        <v>1395.880080084951</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>ANTIARRHYTHMICS</t>
+          <t>MISC. ANTIVIRALS</t>
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>405978.3514136001</v>
+        <v>146932.2941803307</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>108.1413547605109</v>
+        <v>473.1751484562236</v>
       </c>
     </row>
     <row r="60">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>OPIOID AGONISTS &amp; COMBOS</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>400612.4933541996</v>
+        <v>137898.3773441081</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>182.4815355620256</v>
+        <v>1894.11775226041</v>
       </c>
     </row>
     <row r="61">
@@ -4553,13 +4553,13 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.770490677581</v>
+        <v>3475.77049067758</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>1879.236665364516</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062584</v>
+        <v>40.88056000062586</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>83.0773327558841</v>
@@ -4568,7 +4568,7 @@
         <v>5478.965048798607</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310845</v>
+        <v>4130.131957310844</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>2671.817886250133</v>
@@ -4577,13 +4577,13 @@
         <v>54.47014864180036</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>91.05240222120837</v>
+        <v>91.05240222120834</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423987</v>
+        <v>6947.472394423986</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>4273.151023763352</v>
+        <v>4273.151023763351</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>2806.341432842155</v>
@@ -4602,14 +4602,14 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>SEDATIVE HYPNOTICS</t>
+          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>400544.4827065277</v>
+        <v>104069.6574029457</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>178.1609603833926</v>
+        <v>272.1384864083959</v>
       </c>
     </row>
     <row r="62">
@@ -4683,14 +4683,14 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>331091.2838799803</v>
+        <v>89076.01605878503</v>
       </c>
       <c r="AH62" s="56" t="n">
-        <v>112.8666877814321</v>
+        <v>330.5085322076429</v>
       </c>
     </row>
     <row r="63">
@@ -4718,10 +4718,10 @@
         <v>2399.052334449065</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>7534.447042779487</v>
+        <v>7534.44704277949</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171321</v>
+        <v>33.57613890171318</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
@@ -4733,45 +4733,45 @@
         <v>2826.131680913324</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>8372.244019693293</v>
+        <v>8372.244019693282</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.46397792001801</v>
+        <v>40.463977920018</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844697</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11470.1928398111</v>
+        <v>11470.19283981109</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3333.582500652556</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>9331.146765395893</v>
+        <v>9331.146765395886</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>48.29562868547174</v>
+        <v>48.29562868547177</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>250.490735587756</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12963.51563032168</v>
+        <v>12963.51563032167</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>INSULIN ADMINISTRATION SUPPLIES</t>
+          <t>POTASSIUM REMOVING AGENTS</t>
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>321152.7631130893</v>
+        <v>81606.1677792691</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>139.1090109159094</v>
+        <v>130.8563425551474</v>
       </c>
     </row>
     <row r="64">
@@ -4845,14 +4845,14 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>OPHTHALMIC INTEGRIN ANTAGONIST</t>
+          <t>OPIOID AGONISTS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>268732.7076555117</v>
+        <v>74140.76287963479</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>49.17758916476652</v>
+        <v>182.4815355620256</v>
       </c>
     </row>
     <row r="65">
@@ -4931,14 +4931,14 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>OPHTHALMIC PROSTAGLANDINS</t>
+          <t>SEDATIVE HYPNOTICS</t>
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>235211.6011917363</v>
+        <v>73409.45819618384</v>
       </c>
       <c r="AH65" s="56" t="n">
-        <v>229.4341204836981</v>
+        <v>178.1609603833926</v>
       </c>
     </row>
     <row r="66">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>OPHTHALMIC PROSTAGLANDINS</t>
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>229900.5894277587</v>
+        <v>73120.02344159163</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>457.5545255467092</v>
+        <v>229.4341204836981</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -5057,10 +5057,10 @@
         <v>193.8046836844156</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>3230.919246817511</v>
+        <v>3230.91924681751</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>1376.52034078133</v>
+        <v>1376.520340781329</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>474.1870466229238</v>
@@ -5087,21 +5087,21 @@
         <v>208.2943256733983</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>2125.808464910487</v>
+        <v>2125.808464910488</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>BASAL &amp; GLP-1 COMBO</t>
+          <t>ANTIARRHYTHMICS</t>
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>214107.1140619605</v>
+        <v>72979.47865189175</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>49.84702878379795</v>
+        <v>108.1413547605109</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5138,13 +5138,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>35422.05789572736</v>
+        <v>35422.05789572737</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>13995.20182096432</v>
+        <v>13995.20182096431</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -5153,13 +5153,13 @@
         <v>1900.058258153955</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>37084.87478692562</v>
+        <v>37084.87478692561</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>21605.89140012008</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>15097.20885202127</v>
+        <v>15097.20885202126</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>143.8256323506509</v>
@@ -5168,21 +5168,21 @@
         <v>1997.87208359685</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>38846.50756897045</v>
+        <v>38846.50756897044</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
       </c>
       <c r="AF68" s="82" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - MISC.</t>
+          <t>ATYPICAL ANTIPSYCHOTICS</t>
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>204579.7763993455</v>
+        <v>67946.46727132701</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>62.98412967931282</v>
+        <v>188.8163368822109</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -5336,7 +5336,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.75051817676518</v>
+        <v>7.750518176765183</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -5604,7 +5604,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755256</v>
+        <v>7197.985321755258</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -5619,13 +5619,13 @@
         <v>9732.017604071891</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8157.149229625106</v>
+        <v>8157.14922962511</v>
       </c>
       <c r="Q75" s="131" t="n">
         <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.95867935544807</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -5634,7 +5634,7 @@
         <v>11147.09612701664</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9996.096520677065</v>
+        <v>9996.096520677067</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3404.183159089577</v>
@@ -5762,10 +5762,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>232.6051624475786</v>
+        <v>232.6051624475787</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>232.6051624475786</v>
+        <v>232.6051624475787</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -5872,10 +5872,10 @@
         <v>4438</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2209.56854990732</v>
+        <v>2209.568549907321</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>2593.333683184456</v>
+        <v>2593.333683184457</v>
       </c>
       <c r="L79" s="131" t="n">
         <v>10.83583126299182</v>
@@ -5884,7 +5884,7 @@
         <v>26.18930320257346</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>4839.927367557341</v>
+        <v>4839.927367557343</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2292.902614467378</v>
@@ -5902,7 +5902,7 @@
         <v>4995.003831312751</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2339.927961197536</v>
+        <v>2339.927961197535</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2717.102643076893</v>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>2912.438830875361</v>
+        <v>2912.43883087536</v>
       </c>
     </row>
     <row r="90">
@@ -6678,7 +6678,7 @@
         <v>9604.744793221946</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>7.468734608523377</v>
+        <v>7.468734608523375</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>0</v>
@@ -6690,10 +6690,10 @@
         <v>9612.213527830469</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>9711.100612668351</v>
+        <v>9711.100612668355</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -6702,10 +6702,10 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>9718.782032960185</v>
+        <v>9718.782032960189</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473897</v>
+        <v>9788.465905473899</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>7.841870691875751</v>
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165773</v>
+        <v>9796.307776165775</v>
       </c>
     </row>
     <row r="92">
@@ -6809,7 +6809,7 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173873</v>
+        <v>8942.039540173875</v>
       </c>
       <c r="K93" s="131" t="n">
         <v>3500.537314860515</v>
@@ -6824,13 +6824,13 @@
         <v>12582.48366843823</v>
       </c>
       <c r="P93" s="130" t="n">
-        <v>9792.362202164184</v>
+        <v>9792.362202164188</v>
       </c>
       <c r="Q93" s="131" t="n">
         <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888918</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>62.2499783240786</v>
@@ -6842,7 +6842,7 @@
         <v>11405.71069303371</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4368.403547057688</v>
+        <v>4368.403547057689</v>
       </c>
       <c r="X93" s="131" t="n">
         <v>106.4689901288691</v>
@@ -6982,10 +6982,10 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1698.361346924145</v>
+        <v>1698.361346924144</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>1698.361346924145</v>
+        <v>1698.361346924144</v>
       </c>
     </row>
     <row r="96">
@@ -7080,10 +7080,10 @@
         <v>5685.3390405849</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>4472.570348548972</v>
+        <v>4472.570348548973</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>51.71639126361766</v>
+        <v>51.71639126361767</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>109.2666359584576</v>
@@ -7092,7 +7092,7 @@
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778224</v>
+        <v>6423.034571778222</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
@@ -7101,13 +7101,13 @@
         <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>118.6178170830754</v>
+        <v>118.6178170830753</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>11942.47622573674</v>
+        <v>11942.47622573673</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6613.078984960888</v>
+        <v>6613.078984960886</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>5523.444075919049</v>
@@ -7241,7 +7241,7 @@
         <v>11470.90211011721</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>3333.582500652556</v>
+        <v>3333.582500652527</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>9331.146765395853</v>
@@ -7250,10 +7250,10 @@
         <v>48.29562868547146</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>251.2530014457657</v>
+        <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>12964.27789617965</v>
+        <v>12964.27789617962</v>
       </c>
     </row>
     <row r="100">
@@ -7492,7 +7492,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.2085919510268</v>
+        <v>522.208591951027</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -7589,7 +7589,7 @@
         <v>3845.468296768772</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>2747.025908881709</v>
+        <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>511291.1640661132</v>
@@ -8616,19 +8616,19 @@
       </c>
       <c r="AF25" s="44" t="inlineStr">
         <is>
-          <t>BREZTRI AEROSPHERE</t>
+          <t>MOUNJARO</t>
         </is>
       </c>
       <c r="AG25" s="44" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>5985556.120187723</v>
+        <v>5730185.213893273</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>1266.711874538585</v>
+        <v>8128.782825788128</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -8664,7 +8664,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454168</v>
+        <v>96.12539893454166</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -8693,19 +8693,19 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>MOUNJARO</t>
+          <t>DUPIXENT</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>5730185.213893273</v>
+        <v>933136.809174638</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>8128.782825788127</v>
+        <v>720.7293338956135</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -8770,19 +8770,19 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>GEMTESA</t>
+          <t>HUMIRA PEN</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>3661141.896046815</v>
+        <v>848824.7660158189</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>684.9758132507401</v>
+        <v>193.3559319210432</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -8818,7 +8818,7 @@
         <v>2178510</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>56.5609310394383</v>
+        <v>56.56093103943829</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>44.72499948674783</v>
@@ -8847,19 +8847,19 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>CREON</t>
+          <t>BREZTRI AEROSPHERE</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1806648.890686238</v>
+        <v>744415.3999175888</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>189.0163963692158</v>
+        <v>1266.711874538585</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -8924,19 +8924,19 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>STIOLTO RESPIMAT</t>
+          <t>SKYRIZI PEN</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>1513547.932961226</v>
+        <v>693324.4762213475</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>407.19870304802</v>
+        <v>79.45136733018217</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -8972,7 +8972,7 @@
         <v>2277007</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>55.339626796155</v>
+        <v>55.33962679615498</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>45.12946189673967</v>
@@ -9001,19 +9001,19 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>SPIRIVA RESPIMAT</t>
+          <t>TRULICITY</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>1106972.451632788</v>
+        <v>581866.6305464627</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>336.8254182951961</v>
+        <v>849.15899935381</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -9064,19 +9064,19 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>ZENPEP</t>
+          <t>SKYRIZI</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>1083091.030850666</v>
+        <v>486720.9156261383</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>42.85836894418266</v>
+        <v>55.47601779397877</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -9135,19 +9135,19 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>PAXLOVID</t>
+          <t>GEMTESA</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>MISC. ANTIVIRALS</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>1005900.240156003</v>
+        <v>445931.5006842999</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>396.183023183259</v>
+        <v>684.9758132507401</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -9212,19 +9212,19 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>DUPIXENT</t>
+          <t>ERLEADA</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>933136.809174638</v>
+        <v>355309.5792497333</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>720.7293338956135</v>
+        <v>75.13920256966769</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>HUMIRA PEN</t>
+          <t>RINVOQ</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>848824.7660158189</v>
+        <v>311534.8095318336</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>193.3559319210432</v>
+        <v>96.74290112363829</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -9366,19 +9366,19 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>SKYRIZI PEN</t>
+          <t>CREON</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>693324.4762213475</v>
+        <v>226853.0700602088</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>79.45136733018217</v>
+        <v>189.0163963692158</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -9443,19 +9443,19 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>MULTAQ</t>
+          <t>COSENTYX UNOREADY</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>ANTIARRHYTHMICS</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>628835.3616446038</v>
+        <v>207831.890084396</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>107.3919351720206</v>
+        <v>43.33691470295992</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -9520,19 +9520,19 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>TRULICITY</t>
+          <t>STIOLTO RESPIMAT</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>581866.6305464627</v>
+        <v>188350.7026420806</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>849.15899935381</v>
+        <v>407.19870304802</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -9597,19 +9597,19 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>BELSOMRA</t>
+          <t>COSENTYX SENSOREADY PEN</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>SEDATIVE HYPNOTICS</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>580511.3582422143</v>
+        <v>155432.1673017843</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>165.7698655887277</v>
+        <v>37.11859268194824</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="AN38" s="58" t="n">
-        <v>85.34736749332887</v>
+        <v>85.34736749332886</v>
       </c>
     </row>
     <row r="39">
@@ -9660,19 +9660,19 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>ROCKLATAN</t>
+          <t>FREESTYLE LIBRE 3 PLUS/SENSOR/GLUCOSE MONITORING SYSTEM</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>579573.764089913</v>
+        <v>152400.1479959225</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>185.1255532700433</v>
+        <v>1820.8212932262</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -9727,19 +9727,19 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>XTAMPZA ER</t>
+          <t>SPIRIVA RESPIMAT</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>OPIOID AGONISTS &amp; COMBOS</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>557195.9518744365</v>
+        <v>137885.5031571705</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>163.1403176078065</v>
+        <v>336.8254182951961</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -9804,19 +9804,19 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>SKYRIZI</t>
+          <t>ZENPEP</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>486557.5954594493</v>
+        <v>134239.4484458239</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>55.47601779397878</v>
+        <v>42.85836894418266</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -9881,19 +9881,19 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>LOKELMA</t>
+          <t>PAXLOVID</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>POTASSIUM REMOVING AGENTS</t>
+          <t>MISC. ANTIVIRALS</t>
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>484751.9543567373</v>
+        <v>127272.8777518657</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>107.0458507543447</v>
+        <v>396.1830231832591</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -9958,19 +9958,19 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>OMNIPOD 5 DEXCOM G7G6 PODS (GEN 5)</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>INSULIN ADMINISTRATION SUPPLIES</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>451155.7799288999</v>
+        <v>97949.9705912668</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>141.8911911342275</v>
+        <v>244.5277599790226</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -10035,19 +10035,19 @@
       </c>
       <c r="AF44" s="82" t="inlineStr">
         <is>
-          <t>XIIDRA</t>
+          <t>EMGALITY</t>
         </is>
       </c>
       <c r="AG44" s="82" t="inlineStr">
         <is>
-          <t>OPHTHALMIC INTEGRIN ANTAGONIST</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>392563.3474980761</v>
+        <v>97468.66927350093</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>46.22939269433877</v>
+        <v>220.4806199609516</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -10077,7 +10077,7 @@
         <v>2038</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>72790.87999999999</v>
+        <v>72790.88</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>108490</v>
@@ -10214,14 +10214,14 @@
       </c>
       <c r="AF49" s="44" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>7652581.151979812</v>
+        <v>6312051.844439737</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>1816.7771680026</v>
+        <v>8977.941825141937</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -10230,14 +10230,14 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>6312051.844439737</v>
+        <v>2960165.782026018</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>8977.941825141937</v>
+        <v>658.3602571987988</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -10276,14 +10276,14 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>3661141.896046815</v>
+        <v>952060.7077270849</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>685.0910599231772</v>
+        <v>1816.7771680026</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -10397,14 +10397,14 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>2960002.461859329</v>
+        <v>933136.8091746379</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>658.3602571987988</v>
+        <v>726.2533367258893</v>
       </c>
     </row>
     <row r="53">
@@ -10432,7 +10432,7 @@
         <v>1360.461874663778</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>1442.583703144494</v>
+        <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>16.81060051458184</v>
@@ -10441,7 +10441,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="129" t="n">
-        <v>2819.856178322854</v>
+        <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
         <v>1374.950469289653</v>
@@ -10471,21 +10471,21 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>2899.923685528718</v>
+        <v>2899.923685528717</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>2889739.921536905</v>
+        <v>445931.5006842999</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>231.8747653133985</v>
+        <v>685.0910599231772</v>
       </c>
     </row>
     <row r="54">
@@ -10559,14 +10559,14 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>1208649.970156738</v>
+        <v>361092.5185060328</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>381.6103836297688</v>
+        <v>231.8747653133985</v>
       </c>
     </row>
     <row r="55">
@@ -10594,7 +10594,7 @@
         <v>9604.744793221946</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>7.468734608523377</v>
+        <v>7.468734608523375</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>0</v>
@@ -10606,10 +10606,10 @@
         <v>9612.213527830469</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>9711.100612668351</v>
+        <v>9711.100612668355</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -10618,10 +10618,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>9718.782032960185</v>
+        <v>9718.782032960189</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473897</v>
+        <v>9788.465905473899</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>7.841870691875751</v>
@@ -10633,21 +10633,21 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165773</v>
+        <v>9796.307776165775</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>MISC. ANTIVIRALS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>1200382.571187752</v>
+        <v>355309.5792497333</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>471.8360627860924</v>
+        <v>115.9931226550358</v>
       </c>
     </row>
     <row r="56">
@@ -10721,14 +10721,14 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>933136.8091746379</v>
+        <v>267747.4930312645</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>726.2533367258893</v>
+        <v>494.4883268488395</v>
       </c>
     </row>
     <row r="57">
@@ -10765,7 +10765,7 @@
         <v>41.96486816008204</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>2850.466064366342</v>
+        <v>2850.466064366343</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>1635.212972539078</v>
@@ -10786,7 +10786,7 @@
         <v>1409.614172356645</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>964.2203879681115</v>
+        <v>964.2203879681116</v>
       </c>
       <c r="X57" s="131" t="n">
         <v>9.804214882119291</v>
@@ -10802,14 +10802,14 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
+          <t>BASAL INSULIN</t>
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>828352.7490460253</v>
+        <v>164235.0823963753</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>269.4497581626809</v>
+        <v>1565.744525013994</v>
       </c>
     </row>
     <row r="58">
@@ -10883,14 +10883,14 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>POTASSIUM REMOVING AGENTS</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>719977.8296387196</v>
+        <v>162952.3469854508</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>147.5496861749075</v>
+        <v>1941.053990161422</v>
       </c>
     </row>
     <row r="59">
@@ -10954,24 +10954,24 @@
         <v>0</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>1395.880080084952</v>
+        <v>1395.880080084951</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>1395.880080084952</v>
+        <v>1395.880080084951</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>INSULIN ADMINISTRATION SUPPLIES</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>673353.8716046164</v>
+        <v>160695.8279057257</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>194.7526152822731</v>
+        <v>381.6103836297688</v>
       </c>
     </row>
     <row r="60">
@@ -11045,14 +11045,14 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>ANTIARRHYTHMICS</t>
+          <t>MISC. ANTIVIRALS</t>
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>628835.3616446038</v>
+        <v>151880.0156708932</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>107.3919351720206</v>
+        <v>471.8360627860924</v>
       </c>
     </row>
     <row r="61">
@@ -11077,13 +11077,13 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.770490677581</v>
+        <v>3475.77049067758</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>1879.236665364516</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062584</v>
+        <v>40.88056000062586</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>83.0773327558841</v>
@@ -11092,7 +11092,7 @@
         <v>5478.965048798607</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310845</v>
+        <v>4130.131957310844</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>2671.817886250133</v>
@@ -11101,13 +11101,13 @@
         <v>54.47014864180036</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>91.05240222120837</v>
+        <v>91.05240222120834</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423987</v>
+        <v>6947.472394423986</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>4273.151023763352</v>
+        <v>4273.151023763351</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>2806.341432842155</v>
@@ -11126,14 +11126,14 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>SEDATIVE HYPNOTICS</t>
+          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>580511.3582422142</v>
+        <v>109317.3277082409</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>165.7698655887277</v>
+        <v>269.4497581626809</v>
       </c>
     </row>
     <row r="62">
@@ -11207,14 +11207,14 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>OPIOID AGONISTS &amp; COMBOS</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>557195.9518744365</v>
+        <v>97949.9705912668</v>
       </c>
       <c r="AH62" s="56" t="n">
-        <v>163.1403176078065</v>
+        <v>337.7628504760763</v>
       </c>
     </row>
     <row r="63">
@@ -11242,10 +11242,10 @@
         <v>2399.052334449065</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>7534.447042779487</v>
+        <v>7534.44704277949</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171321</v>
+        <v>33.57613890171318</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
@@ -11257,45 +11257,45 @@
         <v>2826.131680913324</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>8372.244019693293</v>
+        <v>8372.244019693282</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.46397792001801</v>
+        <v>40.463977920018</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844697</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11470.1928398111</v>
+        <v>11470.19283981109</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3333.582500652556</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>9331.146765395893</v>
+        <v>9331.146765395886</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>48.29562868547174</v>
+        <v>48.29562868547177</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>250.490735587756</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12963.51563032168</v>
+        <v>12963.51563032167</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>OPHTHALMIC INTEGRIN ANTAGONIST</t>
+          <t>POTASSIUM REMOVING AGENTS</t>
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>392563.3474980761</v>
+        <v>97901.5003026739</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>46.22939269433877</v>
+        <v>147.5496861749075</v>
       </c>
     </row>
     <row r="64">
@@ -11369,14 +11369,14 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>INSULIN ADMINISTRATION SUPPLIES</t>
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>355309.5792497333</v>
+        <v>83150.24558901698</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>115.9931226550358</v>
+        <v>194.7526152822731</v>
       </c>
     </row>
     <row r="65">
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>324112.9073028943</v>
+        <v>77510.65745486059</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>199.6426500422856</v>
@@ -11537,14 +11537,14 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>BASAL &amp; GLP-1 COMBO</t>
+          <t>ANTIARRHYTHMICS</t>
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>318193.1108691014</v>
+        <v>77072.00421791642</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>47.58497061758919</v>
+        <v>107.3919351720206</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -11581,10 +11581,10 @@
         <v>193.8046836844156</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>3230.919246817511</v>
+        <v>3230.91924681751</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>1376.52034078133</v>
+        <v>1376.520340781329</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>474.1870466229238</v>
@@ -11611,21 +11611,21 @@
         <v>208.2943256733983</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>2125.808464910487</v>
+        <v>2125.808464910488</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - MISC.</t>
+          <t>SEDATIVE HYPNOTICS</t>
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>296610.8024133226</v>
+        <v>72672.01399306676</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>58.87096399088956</v>
+        <v>165.7698655887277</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -11662,13 +11662,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>35422.05789572736</v>
+        <v>35422.05789572737</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>13995.20182096432</v>
+        <v>13995.20182096431</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -11677,13 +11677,13 @@
         <v>1900.058258153955</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>37084.87478692562</v>
+        <v>37084.87478692561</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>21605.89140012008</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>15097.20885202127</v>
+        <v>15097.20885202126</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>143.8256323506509</v>
@@ -11692,21 +11692,21 @@
         <v>1997.87208359685</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>38846.50756897045</v>
+        <v>38846.50756897044</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
       </c>
       <c r="AF68" s="82" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>OPIOID AGONISTS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>255697.6936181684</v>
+        <v>70499.96553907912</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>494.4883268488395</v>
+        <v>163.1403176078065</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -11860,7 +11860,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.75051817676518</v>
+        <v>7.750518176765183</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -12128,7 +12128,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755256</v>
+        <v>7197.985321755258</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -12143,13 +12143,13 @@
         <v>9732.017604071891</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8157.149229625106</v>
+        <v>8157.14922962511</v>
       </c>
       <c r="Q75" s="131" t="n">
         <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.95867935544807</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -12158,7 +12158,7 @@
         <v>11147.09612701664</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9996.096520677065</v>
+        <v>9996.096520677067</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3404.183159089577</v>
@@ -12286,10 +12286,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>232.6051624475786</v>
+        <v>232.6051624475787</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>232.6051624475786</v>
+        <v>232.6051624475787</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -12396,10 +12396,10 @@
         <v>4438</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2209.56854990732</v>
+        <v>2209.568549907321</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>2593.333683184456</v>
+        <v>2593.333683184457</v>
       </c>
       <c r="L79" s="131" t="n">
         <v>10.83583126299182</v>
@@ -12408,7 +12408,7 @@
         <v>26.18930320257346</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>4839.927367557341</v>
+        <v>4839.927367557343</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2292.902614467378</v>
@@ -12426,7 +12426,7 @@
         <v>4995.003831312751</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2339.927961197536</v>
+        <v>2339.927961197535</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2717.102643076893</v>
@@ -13107,7 +13107,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>2912.438830875361</v>
+        <v>2912.43883087536</v>
       </c>
     </row>
     <row r="90">
@@ -13202,7 +13202,7 @@
         <v>9604.744793221946</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>7.468734608523377</v>
+        <v>7.468734608523375</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>0</v>
@@ -13214,10 +13214,10 @@
         <v>9612.213527830469</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>9711.100612668351</v>
+        <v>9711.100612668355</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -13226,10 +13226,10 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>9718.782032960185</v>
+        <v>9718.782032960189</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473897</v>
+        <v>9788.465905473899</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>7.841870691875751</v>
@@ -13241,7 +13241,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165773</v>
+        <v>9796.307776165775</v>
       </c>
     </row>
     <row r="92">
@@ -13333,7 +13333,7 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173873</v>
+        <v>8942.039540173875</v>
       </c>
       <c r="K93" s="131" t="n">
         <v>3500.537314860515</v>
@@ -13348,13 +13348,13 @@
         <v>12582.48366843823</v>
       </c>
       <c r="P93" s="130" t="n">
-        <v>9792.362202164184</v>
+        <v>9792.362202164188</v>
       </c>
       <c r="Q93" s="131" t="n">
         <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888918</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>62.2499783240786</v>
@@ -13366,7 +13366,7 @@
         <v>11405.71069303371</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4368.403547057688</v>
+        <v>4368.403547057689</v>
       </c>
       <c r="X93" s="131" t="n">
         <v>106.4689901288691</v>
@@ -13506,10 +13506,10 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1698.361346924145</v>
+        <v>1698.361346924144</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>1698.361346924145</v>
+        <v>1698.361346924144</v>
       </c>
     </row>
     <row r="96">
@@ -13604,10 +13604,10 @@
         <v>5685.3390405849</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>4472.570348548972</v>
+        <v>4472.570348548973</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>51.71639126361766</v>
+        <v>51.71639126361767</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>109.2666359584576</v>
@@ -13616,7 +13616,7 @@
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778224</v>
+        <v>6423.034571778222</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
@@ -13625,13 +13625,13 @@
         <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>118.6178170830754</v>
+        <v>118.6178170830753</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>11942.47622573674</v>
+        <v>11942.47622573673</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6613.078984960888</v>
+        <v>6613.078984960886</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>5523.444075919049</v>
@@ -13765,7 +13765,7 @@
         <v>11470.90211011721</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>3333.582500652556</v>
+        <v>3333.582500652527</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>9331.146765395853</v>
@@ -13774,10 +13774,10 @@
         <v>48.29562868547146</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>251.2530014457657</v>
+        <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>12964.27789617965</v>
+        <v>12964.27789617962</v>
       </c>
     </row>
     <row r="100">
@@ -14016,7 +14016,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.2085919510268</v>
+        <v>522.208591951027</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -14113,7 +14113,7 @@
         <v>3845.468296768772</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>2747.025908881709</v>
+        <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>511291.1640661132</v>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>26031491.31634747</v>
+        <v>7105821.76904021</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>9754.527377416773</v>
@@ -15188,7 +15188,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454168</v>
+        <v>96.12539893454166</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -15217,19 +15217,19 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>BREZTRI AEROSPHERE</t>
+          <t>DUPIXENT</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>8293976.262802305</v>
+        <v>1179873.571167542</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>1325.081957717323</v>
+        <v>867.3273413215642</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -15294,19 +15294,19 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>GEMTESA</t>
+          <t>HUMIRA PEN</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>4837914.059293424</v>
+        <v>867055.9046235287</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>685.3046016411006</v>
+        <v>198.8598248082519</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -15342,7 +15342,7 @@
         <v>2178510</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>56.5609310394383</v>
+        <v>56.56093103943829</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>44.72499948674783</v>
@@ -15371,19 +15371,19 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>DUPIXENT</t>
+          <t>SKYRIZI PEN</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>4389395.08433973</v>
+        <v>854042.6316084283</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>867.3273413215641</v>
+        <v>92.42565264264738</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -15448,19 +15448,19 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>HUMIRA PEN</t>
+          <t>BREZTRI AEROSPHERE</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>3344994.18744099</v>
+        <v>825753.8079507775</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>198.8598248082519</v>
+        <v>1325.081957717323</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -15496,7 +15496,7 @@
         <v>2277007</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>55.339626796155</v>
+        <v>55.33962679615498</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>45.12946189673967</v>
@@ -15525,19 +15525,19 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>SKYRIZI PEN</t>
+          <t>TRULICITY</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>3294790.593459362</v>
+        <v>667647.1117426906</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>92.42565264264738</v>
+        <v>942.5664892827294</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -15588,19 +15588,19 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>CREON</t>
+          <t>SKYRIZI</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>2481679.872471963</v>
+        <v>636335.3291557736</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>194.7114603918203</v>
+        <v>66.11298944579626</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -15659,19 +15659,19 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>TRULICITY</t>
+          <t>GEMTESA</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>2464720.331981408</v>
+        <v>469493.7465181152</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>942.5664892827294</v>
+        <v>685.3046016411006</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -15736,19 +15736,19 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>SKYRIZI</t>
+          <t>ERLEADA</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>2278206.838089314</v>
+        <v>400597.8733939391</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>66.11298944579626</v>
+        <v>79.80835261734684</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -15813,19 +15813,19 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>STIOLTO RESPIMAT</t>
+          <t>RINVOQ</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>2109414.512164751</v>
+        <v>396900.6438973353</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>425.9624192844726</v>
+        <v>114.8941218067131</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -15890,19 +15890,19 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>RINVOQ</t>
+          <t>CREON</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>1531193.478700342</v>
+        <v>249989.5853112747</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>114.8941218067131</v>
+        <v>194.7114603918203</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -15918,7 +15918,7 @@
         </is>
       </c>
       <c r="AN35" s="58" t="n">
-        <v>96.04480653494271</v>
+        <v>96.04480653494272</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickTop="1">
@@ -15967,19 +15967,19 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>ERLEADA</t>
+          <t>COSENTYX UNOREADY</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>1525413.516935095</v>
+        <v>222729.4615631257</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>79.80835261734684</v>
+        <v>44.48750978832351</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -16044,19 +16044,19 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>SPIRIVA RESPIMAT</t>
+          <t>STIOLTO RESPIMAT</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>1513129.438528118</v>
+        <v>210168.6806140575</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>345.2595267693077</v>
+        <v>425.9624192844726</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -16121,19 +16121,19 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>ZENPEP</t>
+          <t>FREESTYLE LIBRE 3 PLUS/SENSOR/GLUCOSE MONITORING SYSTEM</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>1478030.123766056</v>
+        <v>177615.0210601462</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>44.14969160047089</v>
+        <v>1865.941244872346</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -16184,19 +16184,19 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>PAXLOVID</t>
+          <t>COSENTYX SENSOREADY PEN</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>MISC. ANTIVIRALS</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1320925.709691035</v>
+        <v>168220.6477232246</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>394.2773828417476</v>
+        <v>38.12369376989282</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -16251,19 +16251,19 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>COSENTYX UNOREADY</t>
+          <t>SPIRIVA RESPIMAT</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>859262.649994875</v>
+        <v>150933.0726627155</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>44.48750978832351</v>
+        <v>345.2595267693078</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -16328,19 +16328,19 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>OMNIPOD 5 DEXCOM G7G6 PODS (GEN 5)</t>
+          <t>ZENPEP</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>INSULIN ADMINISTRATION SUPPLIES</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>814758.0703815387</v>
+        <v>146527.7963781237</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>198.6476675879186</v>
+        <v>44.14969160047088</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -16405,19 +16405,19 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>ROCKLATAN</t>
+          <t>PAXLOVID</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
+          <t>MISC. ANTIVIRALS</t>
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>761068.8036925427</v>
+        <v>134303.0481042718</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>183.2965128037353</v>
+        <v>394.2773828417476</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -16482,19 +16482,19 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>LOKELMA</t>
+          <t>EMGALITY</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>POTASSIUM REMOVING AGENTS</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>695646.4815579668</v>
+        <v>112561.548182172</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>120.4629776878943</v>
+        <v>237.6692890931074</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -16559,19 +16559,19 @@
       </c>
       <c r="AF44" s="82" t="inlineStr">
         <is>
-          <t>XTAMPZA ER</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="AG44" s="82" t="inlineStr">
         <is>
-          <t>OPIOID AGONISTS &amp; COMBOS</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>673301.9359888579</v>
+        <v>108144.2380230372</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>145.1834628487152</v>
+        <v>251.9589586047851</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -16601,7 +16601,7 @@
         <v>2038</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>72790.87999999999</v>
+        <v>72790.88</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>108490</v>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>28496211.64832888</v>
+        <v>7773468.880782901</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>10697.0938666995</v>
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>12910310.32509213</v>
+        <v>3392282.751003671</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>707.4068275609242</v>
@@ -16800,14 +16800,14 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>10616454.40044498</v>
+        <v>1179873.571167542</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>1900.49425990416</v>
+        <v>873.1126254205338</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -16921,14 +16921,14 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>4837914.059293424</v>
+        <v>1057415.785356533</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>685.3351048132804</v>
+        <v>1900.49425990416</v>
       </c>
     </row>
     <row r="53">
@@ -16956,7 +16956,7 @@
         <v>1360.461874663778</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>1442.583703144494</v>
+        <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>16.81060051458184</v>
@@ -16965,7 +16965,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="129" t="n">
-        <v>2819.856178322854</v>
+        <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
         <v>1374.950469289653</v>
@@ -16995,21 +16995,21 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>2899.923685528718</v>
+        <v>2899.923685528717</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>4389395.08433973</v>
+        <v>469493.7465181152</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>873.1126254205338</v>
+        <v>685.3351048132804</v>
       </c>
     </row>
     <row r="54">
@@ -17083,14 +17083,14 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>3959709.996238018</v>
+        <v>400597.8733939391</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>238.8611519922912</v>
+        <v>120.6369622912027</v>
       </c>
     </row>
     <row r="55">
@@ -17118,7 +17118,7 @@
         <v>9604.744793221946</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>7.468734608523377</v>
+        <v>7.468734608523375</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>0</v>
@@ -17130,10 +17130,10 @@
         <v>9612.213527830469</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>9711.100612668351</v>
+        <v>9711.100612668355</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -17142,10 +17142,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>9718.782032960185</v>
+        <v>9718.782032960189</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473897</v>
+        <v>9788.465905473899</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>7.841870691875751</v>
@@ -17157,21 +17157,21 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165773</v>
+        <v>9796.307776165775</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>1625544.373019962</v>
+        <v>396517.3816893984</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>376.6070963834845</v>
+        <v>238.8611519922912</v>
       </c>
     </row>
     <row r="56">
@@ -17245,14 +17245,14 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>MISC. ANTIVIRALS</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>1576315.559384916</v>
+        <v>307194.7427928897</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>469.5665313240913</v>
+        <v>533.0386368099751</v>
       </c>
     </row>
     <row r="57">
@@ -17289,7 +17289,7 @@
         <v>41.96486816008204</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>2850.466064366342</v>
+        <v>2850.466064366343</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>1635.212972539078</v>
@@ -17310,7 +17310,7 @@
         <v>1409.614172356645</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>964.2203879681115</v>
+        <v>964.2203879681116</v>
       </c>
       <c r="X57" s="131" t="n">
         <v>9.804214882119291</v>
@@ -17326,14 +17326,14 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>1525413.516935095</v>
+        <v>189916.811226378</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>120.6369622912027</v>
+        <v>1989.153308037623</v>
       </c>
     </row>
     <row r="58">
@@ -17407,14 +17407,14 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>INSULIN ADMINISTRATION SUPPLIES</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1230759.553662714</v>
+        <v>176288.0093516581</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>272.6536613951823</v>
+        <v>376.6070963834845</v>
       </c>
     </row>
     <row r="59">
@@ -17478,24 +17478,24 @@
         <v>0</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>1395.880080084952</v>
+        <v>1395.880080084951</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>1395.880080084952</v>
+        <v>1395.880080084951</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
+          <t>BASAL INSULIN</t>
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1087774.898200001</v>
+        <v>164477.1319849687</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>266.7875945520336</v>
+        <v>1494.471834235357</v>
       </c>
     </row>
     <row r="60">
@@ -17569,14 +17569,14 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>MISC. ANTIVIRALS</t>
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1081034.381664674</v>
+        <v>160269.4101919646</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>533.0386368099751</v>
+        <v>469.5665313240913</v>
       </c>
     </row>
     <row r="61">
@@ -17601,13 +17601,13 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.770490677581</v>
+        <v>3475.77049067758</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>1879.236665364516</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062584</v>
+        <v>40.88056000062586</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>83.0773327558841</v>
@@ -17616,7 +17616,7 @@
         <v>5478.965048798607</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310845</v>
+        <v>4130.131957310844</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>2671.817886250133</v>
@@ -17625,13 +17625,13 @@
         <v>54.47014864180036</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>91.05240222120837</v>
+        <v>91.05240222120834</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423987</v>
+        <v>6947.472394423986</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>4273.151023763352</v>
+        <v>4273.151023763351</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>2806.341432842155</v>
@@ -17650,14 +17650,14 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>POTASSIUM REMOVING AGENTS</t>
+          <t>INSULIN ADMINISTRATION SUPPLIES</t>
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1048770.222938441</v>
+        <v>121423.5980562557</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>166.0435638400704</v>
+        <v>272.6536613951824</v>
       </c>
     </row>
     <row r="62">
@@ -17731,14 +17731,14 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>OPIOID AGONISTS &amp; COMBOS</t>
+          <t>POTASSIUM REMOVING AGENTS</t>
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>673301.9359888578</v>
+        <v>118564.0592184856</v>
       </c>
       <c r="AH62" s="56" t="n">
-        <v>145.1834628487152</v>
+        <v>166.0435638400704</v>
       </c>
     </row>
     <row r="63">
@@ -17766,10 +17766,10 @@
         <v>2399.052334449065</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>7534.447042779487</v>
+        <v>7534.44704277949</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171321</v>
+        <v>33.57613890171318</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
@@ -17781,45 +17781,45 @@
         <v>2826.131680913324</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>8372.244019693293</v>
+        <v>8372.244019693282</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.46397792001801</v>
+        <v>40.463977920018</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844697</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11470.1928398111</v>
+        <v>11470.19283981109</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3333.582500652556</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>9331.146765395893</v>
+        <v>9331.146765395886</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>48.29562868547174</v>
+        <v>48.29562868547177</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>250.490735587756</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12963.51563032168</v>
+        <v>12963.51563032167</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>SEDATIVE HYPNOTICS</t>
+          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>649070.0963232729</v>
+        <v>116993.2762718529</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>145.8247890034719</v>
+        <v>266.7875945520336</v>
       </c>
     </row>
     <row r="64">
@@ -17893,14 +17893,14 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>BASAL INSULIN</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>597089.788981067</v>
+        <v>108144.2380230372</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>1494.471834235357</v>
+        <v>347.5927466644546</v>
       </c>
     </row>
     <row r="65">
@@ -17979,14 +17979,14 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>OPHTHALMIC INTEGRIN ANTAGONIST</t>
+          <t>OPIOID AGONISTS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>503876.2374557166</v>
+        <v>68456.91747415655</v>
       </c>
       <c r="AH65" s="56" t="n">
-        <v>43.81252004427874</v>
+        <v>145.1834628487152</v>
       </c>
     </row>
     <row r="66">
@@ -18061,14 +18061,14 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>BASAL &amp; GLP-1 COMBO</t>
+          <t>SEDATIVE HYPNOTICS</t>
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>410866.16261956</v>
+        <v>65141.46164731044</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>45.41890275507653</v>
+        <v>145.8247890034719</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -18105,10 +18105,10 @@
         <v>193.8046836844156</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>3230.919246817511</v>
+        <v>3230.91924681751</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>1376.52034078133</v>
+        <v>1376.520340781329</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>474.1870466229238</v>
@@ -18135,21 +18135,21 @@
         <v>208.2943256733983</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>2125.808464910487</v>
+        <v>2125.808464910488</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - MISC.</t>
+          <t>OPHTHALMIC INTEGRIN ANTAGONIST</t>
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>365624.4187204172</v>
+        <v>48450.48612646081</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>54.3559156212357</v>
+        <v>43.81252004427873</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -18186,13 +18186,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>35422.05789572736</v>
+        <v>35422.05789572737</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>13995.20182096432</v>
+        <v>13995.20182096431</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -18201,13 +18201,13 @@
         <v>1900.058258153955</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>37084.87478692562</v>
+        <v>37084.87478692561</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>21605.89140012008</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>15097.20885202127</v>
+        <v>15097.20885202126</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>143.8256323506509</v>
@@ -18216,21 +18216,21 @@
         <v>1997.87208359685</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>38846.50756897045</v>
+        <v>38846.50756897044</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
       </c>
       <c r="AF68" s="82" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>BASAL &amp; GLP-1 COMBO</t>
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>346340.9492447305</v>
+        <v>41016.72635343064</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>347.5927466644546</v>
+        <v>45.41890275507653</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -18384,7 +18384,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.75051817676518</v>
+        <v>7.750518176765183</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -18652,7 +18652,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755256</v>
+        <v>7197.985321755258</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -18667,13 +18667,13 @@
         <v>9732.017604071891</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8157.149229625106</v>
+        <v>8157.14922962511</v>
       </c>
       <c r="Q75" s="131" t="n">
         <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.95867935544807</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -18682,7 +18682,7 @@
         <v>11147.09612701664</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9996.096520677065</v>
+        <v>9996.096520677067</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3404.183159089577</v>
@@ -18810,10 +18810,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>232.6051624475786</v>
+        <v>232.6051624475787</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>232.6051624475786</v>
+        <v>232.6051624475787</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -18920,10 +18920,10 @@
         <v>4438</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2209.56854990732</v>
+        <v>2209.568549907321</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>2593.333683184456</v>
+        <v>2593.333683184457</v>
       </c>
       <c r="L79" s="131" t="n">
         <v>10.83583126299182</v>
@@ -18932,7 +18932,7 @@
         <v>26.18930320257346</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>4839.927367557341</v>
+        <v>4839.927367557343</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2292.902614467378</v>
@@ -18950,7 +18950,7 @@
         <v>4995.003831312751</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2339.927961197536</v>
+        <v>2339.927961197535</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2717.102643076893</v>
@@ -19631,7 +19631,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>2912.438830875361</v>
+        <v>2912.43883087536</v>
       </c>
     </row>
     <row r="90">
@@ -19726,7 +19726,7 @@
         <v>9604.744793221946</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>7.468734608523377</v>
+        <v>7.468734608523375</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>0</v>
@@ -19738,10 +19738,10 @@
         <v>9612.213527830469</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>9711.100612668351</v>
+        <v>9711.100612668355</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -19750,10 +19750,10 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>9718.782032960185</v>
+        <v>9718.782032960189</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473897</v>
+        <v>9788.465905473899</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>7.841870691875751</v>
@@ -19765,7 +19765,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165773</v>
+        <v>9796.307776165775</v>
       </c>
     </row>
     <row r="92">
@@ -19857,7 +19857,7 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173873</v>
+        <v>8942.039540173875</v>
       </c>
       <c r="K93" s="131" t="n">
         <v>3500.537314860515</v>
@@ -19872,13 +19872,13 @@
         <v>12582.48366843823</v>
       </c>
       <c r="P93" s="130" t="n">
-        <v>9792.362202164184</v>
+        <v>9792.362202164188</v>
       </c>
       <c r="Q93" s="131" t="n">
         <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888918</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>62.2499783240786</v>
@@ -19890,7 +19890,7 @@
         <v>11405.71069303371</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4368.403547057688</v>
+        <v>4368.403547057689</v>
       </c>
       <c r="X93" s="131" t="n">
         <v>106.4689901288691</v>
@@ -20030,10 +20030,10 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1698.361346924145</v>
+        <v>1698.361346924144</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>1698.361346924145</v>
+        <v>1698.361346924144</v>
       </c>
     </row>
     <row r="96">
@@ -20128,10 +20128,10 @@
         <v>5685.3390405849</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>4472.570348548972</v>
+        <v>4472.570348548973</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>51.71639126361766</v>
+        <v>51.71639126361767</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>109.2666359584576</v>
@@ -20140,7 +20140,7 @@
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778224</v>
+        <v>6423.034571778222</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
@@ -20149,13 +20149,13 @@
         <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>118.6178170830754</v>
+        <v>118.6178170830753</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>11942.47622573674</v>
+        <v>11942.47622573673</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6613.078984960888</v>
+        <v>6613.078984960886</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>5523.444075919049</v>
@@ -20289,7 +20289,7 @@
         <v>11470.90211011721</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>3333.582500652556</v>
+        <v>3333.582500652527</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>9331.146765395853</v>
@@ -20298,10 +20298,10 @@
         <v>48.29562868547146</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>251.2530014457657</v>
+        <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>12964.27789617965</v>
+        <v>12964.27789617962</v>
       </c>
     </row>
     <row r="100">
@@ -20540,7 +20540,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.2085919510268</v>
+        <v>522.208591951027</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -20637,7 +20637,7 @@
         <v>3845.468296768772</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>2747.025908881709</v>
+        <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>511291.1640661132</v>
@@ -21673,7 +21673,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>55194572.44262568</v>
+        <v>8733474.762882363</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>11705.41951788296</v>
@@ -21712,7 +21712,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454168</v>
+        <v>96.12539893454166</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -21741,19 +21741,19 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>BREZTRI AEROSPHERE</t>
+          <t>DUPIXENT</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>10891571.00827633</v>
+        <v>1470248.717945522</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>1386.141734328937</v>
+        <v>1038.059652223579</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -21818,19 +21818,19 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>DUPIXENT</t>
+          <t>SKYRIZI PEN</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>8935897.679002849</v>
+        <v>1038430.264053949</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>1038.059652223579</v>
+        <v>107.1309756533883</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -21866,7 +21866,7 @@
         <v>2178510</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>56.5609310394383</v>
+        <v>56.56093103943829</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>44.72499948674783</v>
@@ -21895,7 +21895,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>SKYRIZI PEN</t>
+          <t>HUMIRA PEN</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -21904,10 +21904,10 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>6571416.296995293</v>
+        <v>898145.1573003263</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>107.1309756533883</v>
+        <v>203.2628537277481</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -21972,19 +21972,19 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>GEMTESA</t>
+          <t>BREZTRI AEROSPHERE</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>6031972.091225914</v>
+        <v>893766.5419403772</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>683.0979208238161</v>
+        <v>1386.141734328937</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -22020,7 +22020,7 @@
         <v>2277007</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>55.339626796155</v>
+        <v>55.33962679615498</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>45.12946189673967</v>
@@ -22049,7 +22049,7 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>HUMIRA PEN</t>
+          <t>SKYRIZI</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>5683661.125889662</v>
+        <v>819026.5537904161</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>203.2628537277481</v>
+        <v>78.27976289350613</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>4840041.07375377</v>
+        <v>759244.4032184778</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1046.24880310383</v>
@@ -22183,7 +22183,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>SKYRIZI</t>
+          <t>RINVOQ</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -22192,10 +22192,10 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>4681156.502381124</v>
+        <v>497866.2856486476</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>78.27976289350613</v>
+        <v>135.615340574128</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -22260,19 +22260,19 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>CREON</t>
+          <t>GEMTESA</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>3231209.203593119</v>
+        <v>482757.4699492153</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>200.1341745637325</v>
+        <v>683.0979208238161</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -22337,19 +22337,19 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>RINVOQ</t>
+          <t>ERLEADA</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>3150607.928609123</v>
+        <v>442725.4012005675</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>135.615340574128</v>
+        <v>84.05734931069438</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -22414,19 +22414,19 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>ERLEADA</t>
+          <t>CREON</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>2761408.691267405</v>
+        <v>268206.8622674547</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>84.05734931069438</v>
+        <v>200.1341745637325</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -22491,19 +22491,19 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>STIOLTO RESPIMAT</t>
+          <t>COSENTYX UNOREADY</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>2204076.959654857</v>
+        <v>234593.1675200218</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>395.8814041868176</v>
+        <v>45.37325610820903</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -22568,19 +22568,19 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>SPIRIVA RESPIMAT</t>
+          <t>STIOLTO RESPIMAT</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>1963284.627870549</v>
+        <v>180996.8510310526</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>353.9048253196112</v>
+        <v>395.8814041868176</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -22645,19 +22645,19 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>ZENPEP</t>
+          <t>COSENTYX SENSOREADY PEN</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>1908741.389280422</v>
+        <v>179208.8089055996</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>45.37926051154399</v>
+        <v>38.90622654596869</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -22708,19 +22708,19 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>PAXLOVID</t>
+          <t>SPIRIVA RESPIMAT</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>MISC. ANTIVIRALS</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1640458.327630619</v>
+        <v>161405.3239243289</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>391.1862481602683</v>
+        <v>353.9048253196112</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -22775,19 +22775,19 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>COSENTYX UNOREADY</t>
+          <t>ZENPEP</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1484557.430160499</v>
+        <v>155974.5375426568</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>45.37325610820903</v>
+        <v>45.37926051154399</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -22852,19 +22852,19 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>OMNIPOD 5 DEXCOM G7G6 PODS (GEN 5)</t>
+          <t>PAXLOVID</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>INSULIN ADMINISTRATION SUPPLIES</t>
+          <t>MISC. ANTIVIRALS</t>
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>1398021.975909639</v>
+        <v>137405.3360044485</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>278.106734623086</v>
+        <v>391.1862481602683</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -22929,19 +22929,19 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>COSENTYX SENSOREADY PEN</t>
+          <t>EMGALITY</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1134072.963946465</v>
+        <v>128330.3430705311</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>38.90622654596869</v>
+        <v>255.2710766433429</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -23006,19 +23006,19 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>ROCKLATAN</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>949489.6934670794</v>
+        <v>117222.0692021536</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>181.4855432572344</v>
+        <v>257.0686862852901</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -23083,19 +23083,19 @@
       </c>
       <c r="AF44" s="82" t="inlineStr">
         <is>
-          <t>LOKELMA</t>
+          <t>OMNIPOD 5 DEXCOM G7G6 PODS (GEN 5)</t>
         </is>
       </c>
       <c r="AG44" s="82" t="inlineStr">
         <is>
-          <t>POTASSIUM REMOVING AGENTS</t>
+          <t>INSULIN ADMINISTRATION SUPPLIES</t>
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>939892.186244019</v>
+        <v>115085.9769406243</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>135.1486192978254</v>
+        <v>278.106734623086</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -23125,7 +23125,7 @@
         <v>2038</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>72790.87999999999</v>
+        <v>72790.88</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>108490</v>
@@ -23266,7 +23266,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>60034613.51637945</v>
+        <v>9492719.166100841</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>12751.66832098679</v>
@@ -23282,7 +23282,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>24375541.8213778</v>
+        <v>3931178.458781892</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>762.9533459135781</v>
@@ -23324,14 +23324,14 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>13337178.6541234</v>
+        <v>1470248.717945522</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>1927.909408130234</v>
+        <v>1044.097471693166</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -23445,14 +23445,14 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>8935897.679002849</v>
+        <v>1094851.488272402</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>1044.097471693166</v>
+        <v>1927.909408130234</v>
       </c>
     </row>
     <row r="53">
@@ -23480,7 +23480,7 @@
         <v>1360.461874663778</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>1442.583703144494</v>
+        <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>16.81060051458184</v>
@@ -23489,7 +23489,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="129" t="n">
-        <v>2819.856178322854</v>
+        <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
         <v>1374.950469289653</v>
@@ -23519,7 +23519,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>2899.923685528718</v>
+        <v>2899.923685528717</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>6031972.091225914</v>
+        <v>482757.4699492153</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>683.1283257757816</v>
@@ -23607,14 +23607,14 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>5139950.59287354</v>
+        <v>442725.4012005675</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>245.5134350752765</v>
+        <v>125.8940904648589</v>
       </c>
     </row>
     <row r="55">
@@ -23642,7 +23642,7 @@
         <v>9604.744793221946</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>7.468734608523377</v>
+        <v>7.468734608523375</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>0</v>
@@ -23654,10 +23654,10 @@
         <v>9612.213527830469</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>9711.100612668351</v>
+        <v>9711.100612668355</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -23666,10 +23666,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>9718.782032960185</v>
+        <v>9718.782032960189</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473897</v>
+        <v>9788.465905473899</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>7.841870691875751</v>
@@ -23681,21 +23681,21 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165773</v>
+        <v>9796.307776165775</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>2761408.691267405</v>
+        <v>424181.3998101114</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>125.8940904648589</v>
+        <v>245.5134350752765</v>
       </c>
     </row>
     <row r="56">
@@ -23769,14 +23769,14 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>INSULIN ADMINISTRATION SUPPLIES</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2138232.360072804</v>
+        <v>347645.2346109536</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>381.7151259532553</v>
+        <v>572.5154782521217</v>
       </c>
     </row>
     <row r="57">
@@ -23813,7 +23813,7 @@
         <v>41.96486816008204</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>2850.466064366342</v>
+        <v>2850.466064366343</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>1635.212972539078</v>
@@ -23834,7 +23834,7 @@
         <v>1409.614172356645</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>964.2203879681115</v>
+        <v>964.2203879681116</v>
       </c>
       <c r="X57" s="131" t="n">
         <v>9.804214882119291</v>
@@ -23850,14 +23850,14 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>2101424.194752911</v>
+        <v>189044.2100013556</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>572.5154782521217</v>
+        <v>380.9868502583004</v>
       </c>
     </row>
     <row r="58">
@@ -23931,14 +23931,14 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>INSULIN ADMINISTRATION SUPPLIES</t>
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>2078564.147371794</v>
+        <v>173840.8646211465</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>380.9868502583005</v>
+        <v>381.7151259532552</v>
       </c>
     </row>
     <row r="59">
@@ -24002,10 +24002,10 @@
         <v>0</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>1395.880080084952</v>
+        <v>1395.880080084951</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>1395.880080084952</v>
+        <v>1395.880080084951</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1957627.115132417</v>
+        <v>163971.4993033075</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>465.8851297185105</v>
@@ -24093,14 +24093,14 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>POTASSIUM REMOVING AGENTS</t>
+          <t>BASAL INSULIN</t>
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1440867.790273658</v>
+        <v>162271.5517406999</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>186.2859347078134</v>
+        <v>1424.694944294909</v>
       </c>
     </row>
     <row r="61">
@@ -24125,13 +24125,13 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.770490677581</v>
+        <v>3475.77049067758</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>1879.236665364516</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062584</v>
+        <v>40.88056000062586</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>83.0773327558841</v>
@@ -24140,7 +24140,7 @@
         <v>5478.965048798607</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310845</v>
+        <v>4130.131957310844</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>2671.817886250133</v>
@@ -24149,13 +24149,13 @@
         <v>54.47014864180036</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>91.05240222120837</v>
+        <v>91.05240222120834</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423987</v>
+        <v>6947.472394423986</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>4273.151023763352</v>
+        <v>4273.151023763351</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>2806.341432842155</v>
@@ -24174,14 +24174,14 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
+          <t>POTASSIUM REMOVING AGENTS</t>
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1356769.998544786</v>
+        <v>140157.5738936824</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>264.1517331178595</v>
+        <v>186.2859347078134</v>
       </c>
     </row>
     <row r="62">
@@ -24255,14 +24255,14 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>BASAL INSULIN</t>
+          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1015176.022450541</v>
+        <v>122183.6559801901</v>
       </c>
       <c r="AH62" s="56" t="n">
-        <v>1424.694944294908</v>
+        <v>264.1517331178595</v>
       </c>
     </row>
     <row r="63">
@@ -24290,10 +24290,10 @@
         <v>2399.052334449065</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>7534.447042779487</v>
+        <v>7534.44704277949</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171321</v>
+        <v>33.57613890171318</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
@@ -24305,45 +24305,45 @@
         <v>2826.131680913324</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>8372.244019693293</v>
+        <v>8372.244019693282</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.46397792001801</v>
+        <v>40.463977920018</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844697</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11470.1928398111</v>
+        <v>11470.19283981109</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3333.582500652556</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>9331.146765395893</v>
+        <v>9331.146765395886</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>48.29562868547174</v>
+        <v>48.29562868547177</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>250.490735587756</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12963.51563032168</v>
+        <v>12963.51563032167</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>OPIOID AGONISTS &amp; COMBOS</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>772110.4486303548</v>
+        <v>117222.0692021536</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>128.4757499440851</v>
+        <v>354.6331001102211</v>
       </c>
     </row>
     <row r="64">
@@ -24417,14 +24417,14 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>OPIOID AGONISTS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>599342.3331044482</v>
+        <v>64672.2283886556</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>354.6331001102211</v>
+        <v>128.4757499440851</v>
       </c>
     </row>
     <row r="65">
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>501801.4774384124</v>
+        <v>41286.7260780431</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>43.29829418544201</v>
@@ -24589,7 +24589,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>438279.2444339501</v>
+        <v>37835.41603874155</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>47.48465002356028</v>
@@ -24629,10 +24629,10 @@
         <v>193.8046836844156</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>3230.919246817511</v>
+        <v>3230.91924681751</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>1376.52034078133</v>
+        <v>1376.520340781329</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>474.1870466229238</v>
@@ -24659,7 +24659,7 @@
         <v>208.2943256733983</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>2125.808464910487</v>
+        <v>2125.808464910488</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -24670,7 +24670,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>421182.1005327893</v>
+        <v>37431.03098405986</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>49.52139328881418</v>
@@ -24710,13 +24710,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>35422.05789572736</v>
+        <v>35422.05789572737</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>13995.20182096432</v>
+        <v>13995.20182096431</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -24725,13 +24725,13 @@
         <v>1900.058258153955</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>37084.87478692562</v>
+        <v>37084.87478692561</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>21605.89140012008</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>15097.20885202127</v>
+        <v>15097.20885202126</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>143.8256323506509</v>
@@ -24740,21 +24740,21 @@
         <v>1997.87208359685</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>38846.50756897045</v>
+        <v>38846.50756897044</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
       </c>
       <c r="AF68" s="82" t="inlineStr">
         <is>
-          <t>VAGINAL ESTROGENS</t>
+          <t>RAPID ACTING</t>
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>362509.3309368407</v>
+        <v>36426.12670616305</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>147.4978289250544</v>
+        <v>259.5143090597786</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -24908,7 +24908,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.75051817676518</v>
+        <v>7.750518176765183</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -25176,7 +25176,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755256</v>
+        <v>7197.985321755258</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -25191,13 +25191,13 @@
         <v>9732.017604071891</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8157.149229625106</v>
+        <v>8157.14922962511</v>
       </c>
       <c r="Q75" s="131" t="n">
         <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.95867935544807</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -25206,7 +25206,7 @@
         <v>11147.09612701664</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9996.096520677065</v>
+        <v>9996.096520677067</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3404.183159089577</v>
@@ -25334,10 +25334,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>232.6051624475786</v>
+        <v>232.6051624475787</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>232.6051624475786</v>
+        <v>232.6051624475787</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -25444,10 +25444,10 @@
         <v>4438</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2209.56854990732</v>
+        <v>2209.568549907321</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>2593.333683184456</v>
+        <v>2593.333683184457</v>
       </c>
       <c r="L79" s="131" t="n">
         <v>10.83583126299182</v>
@@ -25456,7 +25456,7 @@
         <v>26.18930320257346</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>4839.927367557341</v>
+        <v>4839.927367557343</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2292.902614467378</v>
@@ -25474,7 +25474,7 @@
         <v>4995.003831312751</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2339.927961197536</v>
+        <v>2339.927961197535</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2717.102643076893</v>
@@ -26155,7 +26155,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>2912.438830875361</v>
+        <v>2912.43883087536</v>
       </c>
     </row>
     <row r="90">
@@ -26250,7 +26250,7 @@
         <v>9604.744793221946</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>7.468734608523377</v>
+        <v>7.468734608523375</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>0</v>
@@ -26262,10 +26262,10 @@
         <v>9612.213527830469</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>9711.100612668351</v>
+        <v>9711.100612668355</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -26274,10 +26274,10 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>9718.782032960185</v>
+        <v>9718.782032960189</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473897</v>
+        <v>9788.465905473899</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>7.841870691875751</v>
@@ -26289,7 +26289,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165773</v>
+        <v>9796.307776165775</v>
       </c>
     </row>
     <row r="92">
@@ -26381,7 +26381,7 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173873</v>
+        <v>8942.039540173875</v>
       </c>
       <c r="K93" s="131" t="n">
         <v>3500.537314860515</v>
@@ -26396,13 +26396,13 @@
         <v>12582.48366843823</v>
       </c>
       <c r="P93" s="130" t="n">
-        <v>9792.362202164184</v>
+        <v>9792.362202164188</v>
       </c>
       <c r="Q93" s="131" t="n">
         <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888918</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>62.2499783240786</v>
@@ -26414,7 +26414,7 @@
         <v>11405.71069303371</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4368.403547057688</v>
+        <v>4368.403547057689</v>
       </c>
       <c r="X93" s="131" t="n">
         <v>106.4689901288691</v>
@@ -26554,10 +26554,10 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1698.361346924145</v>
+        <v>1698.361346924144</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>1698.361346924145</v>
+        <v>1698.361346924144</v>
       </c>
     </row>
     <row r="96">
@@ -26652,10 +26652,10 @@
         <v>5685.3390405849</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>4472.570348548972</v>
+        <v>4472.570348548973</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>51.71639126361766</v>
+        <v>51.71639126361767</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>109.2666359584576</v>
@@ -26664,7 +26664,7 @@
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778224</v>
+        <v>6423.034571778222</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
@@ -26673,13 +26673,13 @@
         <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>118.6178170830754</v>
+        <v>118.6178170830753</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>11942.47622573674</v>
+        <v>11942.47622573673</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6613.078984960888</v>
+        <v>6613.078984960886</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>5523.444075919049</v>
@@ -26813,7 +26813,7 @@
         <v>11470.90211011721</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>3333.582500652556</v>
+        <v>3333.582500652527</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>9331.146765395853</v>
@@ -26822,10 +26822,10 @@
         <v>48.29562868547146</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>251.2530014457657</v>
+        <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>12964.27789617965</v>
+        <v>12964.27789617962</v>
       </c>
     </row>
     <row r="100">
@@ -27064,7 +27064,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.2085919510268</v>
+        <v>522.208591951027</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -27161,7 +27161,7 @@
         <v>3845.468296768772</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>2747.025908881709</v>
+        <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>511291.1640661132</v>
@@ -28197,7 +28197,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>88039949.20427474</v>
+        <v>10848588.38991465</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>14046.4886195905</v>
@@ -28236,7 +28236,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454168</v>
+        <v>96.12539893454166</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>15499154.4255674</v>
+        <v>1852449.718636751</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1243.579383973071</v>
@@ -28342,19 +28342,19 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>BREZTRI AEROSPHERE</t>
+          <t>SKYRIZI PEN</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>13299089.74676132</v>
+        <v>1278546.023722931</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>1450.015145446814</v>
+        <v>124.4909448484157</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -28390,7 +28390,7 @@
         <v>2178510</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>56.5609310394383</v>
+        <v>56.56093103943829</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>44.72499948674783</v>
@@ -28419,7 +28419,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>SKYRIZI PEN</t>
+          <t>SKYRIZI</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -28428,10 +28428,10 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>11150097.00978213</v>
+        <v>1062938.142193494</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>124.4909448484157</v>
+        <v>92.68558765879806</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -28496,19 +28496,19 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>SKYRIZI</t>
+          <t>BREZTRI AEROSPHERE</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>8198356.252521644</v>
+        <v>969024.957236251</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>92.68558765879806</v>
+        <v>1450.015145446814</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -28544,7 +28544,7 @@
         <v>2277007</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>55.339626796155</v>
+        <v>55.33962679615498</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>45.12946189673967</v>
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>8196471.36851883</v>
+        <v>939863.2018703282</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>207.8023572318635</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>7144035.952028795</v>
+        <v>872627.0500433028</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1161.336171445251</v>
@@ -28707,19 +28707,19 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>GEMTESA</t>
+          <t>RINVOQ</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>6993069.478539776</v>
+        <v>630970.5459043736</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>680.8983455187634</v>
+        <v>160.1194938565857</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -28784,19 +28784,19 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>RINVOQ</t>
+          <t>GEMTESA</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>5502643.367239133</v>
+        <v>499027.60181025</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>160.1194938565857</v>
+        <v>680.8983455187634</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>4246859.930677499</v>
+        <v>494253.4158101933</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>88.53256258799576</v>
@@ -28947,7 +28947,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>3912123.427218268</v>
+        <v>287790.8057988767</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>205.7079113253324</v>
@@ -29015,19 +29015,19 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>ZENPEP</t>
+          <t>COSENTYX UNOREADY</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>2292021.485614128</v>
+        <v>249571.0033078875</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>46.64307291679049</v>
+        <v>46.27663763732347</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -29092,19 +29092,19 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>OMNIPOD 5 DEXCOM G7G6 PODS (GEN 5)</t>
+          <t>COSENTYX SENSOREADY PEN</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>INSULIN ADMINISTRATION SUPPLIES</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2230503.843793887</v>
+        <v>192842.1910730915</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>389.3494284723204</v>
+        <v>39.70692345325912</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -29169,19 +29169,19 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>COSENTYX UNOREADY</t>
+          <t>ZENPEP</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2176488.64106486</v>
+        <v>166414.7962031004</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>46.27663763732347</v>
+        <v>46.64307291679049</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -29232,19 +29232,19 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>PAXLOVID</t>
+          <t>OMNIPOD 5 DEXCOM G7G6 PODS (GEN 5)</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>MISC. ANTIVIRALS</t>
+          <t>INSULIN ADMINISTRATION SUPPLIES</t>
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1894330.110140703</v>
+        <v>162953.2068695604</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>388.1193479746918</v>
+        <v>389.3494284723204</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -29299,19 +29299,19 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>COSENTYX SENSOREADY PEN</t>
+          <t>EMGALITY</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1681761.233579085</v>
+        <v>147816.7472245604</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>39.70692345325912</v>
+        <v>274.1764525795489</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -29376,19 +29376,19 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>LOKELMA</t>
+          <t>PAXLOVID</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>POTASSIUM REMOVING AGENTS</t>
+          <t>MISC. ANTIVIRALS</t>
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>1206179.333007056</v>
+        <v>140413.1279884558</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>151.6245874764233</v>
+        <v>388.1193479746918</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -29453,19 +29453,19 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>EMGALITY</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1154757.534722214</v>
+        <v>128203.2907590142</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>274.1764525795489</v>
+        <v>262.2820392431559</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -29530,19 +29530,19 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>ROCKLATAN</t>
+          <t>LOKELMA</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
+          <t>POTASSIUM REMOVING AGENTS</t>
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1107670.039422355</v>
+        <v>119524.2940068942</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>179.6924660898529</v>
+        <v>151.6245874764233</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -29607,19 +29607,19 @@
       </c>
       <c r="AF44" s="82" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>AIMOVIG</t>
         </is>
       </c>
       <c r="AG44" s="82" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>894687.9131575025</v>
+        <v>104347.4144313622</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>262.2820392431559</v>
+        <v>209.1982181531818</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -29649,7 +29649,7 @@
         <v>2038</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>72790.87999999999</v>
+        <v>72790.88</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>108490</v>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>95183985.15630352</v>
+        <v>11721215.43995796</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>15207.82479103575</v>
@@ -29806,7 +29806,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>39391199.56716329</v>
+        <v>4639721.891568852</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>828.4194522121426</v>
@@ -29852,7 +29852,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>15499154.4255674</v>
+        <v>1852449.718636751</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>1249.889875332569</v>
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>13411654.55961245</v>
+        <v>977368.5808682955</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>1591.449898611768</v>
@@ -30004,7 +30004,7 @@
         <v>1360.461874663778</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>1442.583703144494</v>
+        <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>16.81060051458184</v>
@@ -30013,7 +30013,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="129" t="n">
-        <v>2819.856178322854</v>
+        <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
         <v>1374.950469289653</v>
@@ -30043,7 +30043,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>2899.923685528718</v>
+        <v>2899.923685528717</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -30054,7 +30054,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>6993069.478539776</v>
+        <v>499027.60181025</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>680.9286525667836</v>
@@ -30131,14 +30131,14 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>6204144.912832396</v>
+        <v>494253.4158101933</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>252.3509842421229</v>
+        <v>124.2025011145804</v>
       </c>
     </row>
     <row r="55">
@@ -30166,7 +30166,7 @@
         <v>9604.744793221946</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>7.468734608523377</v>
+        <v>7.468734608523375</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>0</v>
@@ -30178,10 +30178,10 @@
         <v>9612.213527830469</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>9711.100612668351</v>
+        <v>9711.100612668355</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -30190,10 +30190,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>9718.782032960185</v>
+        <v>9718.782032960189</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473897</v>
+        <v>9788.465905473899</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>7.841870691875751</v>
@@ -30205,21 +30205,21 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165773</v>
+        <v>9796.307776165775</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>4246859.930677499</v>
+        <v>454205.6020019772</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>124.2025011145804</v>
+        <v>252.3509842421229</v>
       </c>
     </row>
     <row r="56">
@@ -30293,14 +30293,14 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>INSULIN ADMINISTRATION SUPPLIES</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>3455578.778818662</v>
+        <v>397583.5563320723</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>534.4011763345574</v>
+        <v>614.9159745714738</v>
       </c>
     </row>
     <row r="57">
@@ -30337,7 +30337,7 @@
         <v>41.96486816008204</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>2850.466064366342</v>
+        <v>2850.466064366343</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>1635.212972539078</v>
@@ -30358,7 +30358,7 @@
         <v>1409.614172356645</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>964.2203879681115</v>
+        <v>964.2203879681116</v>
       </c>
       <c r="X57" s="131" t="n">
         <v>9.804214882119291</v>
@@ -30374,14 +30374,14 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>INSULIN ADMINISTRATION SUPPLIES</t>
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>3073408.777683327</v>
+        <v>249760.0623460387</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>614.9159745714738</v>
+        <v>534.4011763345574</v>
       </c>
     </row>
     <row r="58">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>2260582.866484272</v>
+        <v>167560.8225097525</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>462.2325903015174</v>
@@ -30526,24 +30526,24 @@
         <v>0</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>1395.880080084952</v>
+        <v>1395.880080084951</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>1395.880080084952</v>
+        <v>1395.880080084951</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
+          <t>BASAL INSULIN</t>
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1582378.145179326</v>
+        <v>161828.2428141385</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>261.541913994655</v>
+        <v>1358.175937345779</v>
       </c>
     </row>
     <row r="60">
@@ -30617,14 +30617,14 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>BASAL INSULIN</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1299978.099642728</v>
+        <v>128203.2907590142</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>1358.175937345779</v>
+        <v>361.8165997639837</v>
       </c>
     </row>
     <row r="61">
@@ -30649,13 +30649,13 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.770490677581</v>
+        <v>3475.77049067758</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>1879.236665364516</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062584</v>
+        <v>40.88056000062586</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>83.0773327558841</v>
@@ -30664,7 +30664,7 @@
         <v>5478.965048798607</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310845</v>
+        <v>4130.131957310844</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>2671.817886250133</v>
@@ -30673,13 +30673,13 @@
         <v>54.47014864180036</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>91.05240222120837</v>
+        <v>91.05240222120834</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423987</v>
+        <v>6947.472394423986</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>4273.151023763352</v>
+        <v>4273.151023763351</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>2806.341432842155</v>
@@ -30698,14 +30698,14 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>POTASSIUM REMOVING AGENTS</t>
+          <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1206179.333007056</v>
+        <v>127719.5369583425</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>163.6270054127749</v>
+        <v>261.541913994655</v>
       </c>
     </row>
     <row r="62">
@@ -30779,14 +30779,14 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>POTASSIUM REMOVING AGENTS</t>
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>894687.9131575024</v>
+        <v>119524.2940068942</v>
       </c>
       <c r="AH62" s="56" t="n">
-        <v>361.8165997639837</v>
+        <v>163.6270054127749</v>
       </c>
     </row>
     <row r="63">
@@ -30814,10 +30814,10 @@
         <v>2399.052334449065</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>7534.447042779487</v>
+        <v>7534.44704277949</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171321</v>
+        <v>33.57613890171318</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
@@ -30829,45 +30829,45 @@
         <v>2826.131680913324</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>8372.244019693293</v>
+        <v>8372.244019693282</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.46397792001801</v>
+        <v>40.463977920018</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844697</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11470.1928398111</v>
+        <v>11470.19283981109</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3333.582500652556</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>9331.146765395893</v>
+        <v>9331.146765395886</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>48.29562868547174</v>
+        <v>48.29562868547177</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>250.490735587756</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12963.51563032168</v>
+        <v>12963.51563032167</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>OPIOID AGONISTS &amp; COMBOS</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>823289.632386789</v>
+        <v>81267.96943427956</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>113.6907606405198</v>
+        <v>178.3339380167246</v>
       </c>
     </row>
     <row r="64">
@@ -30941,14 +30941,14 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>OPIOID AGONISTS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>818769.4289649995</v>
+        <v>61024.56583731784</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>178.3339380167246</v>
+        <v>113.6907606405198</v>
       </c>
     </row>
     <row r="65">
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>592331.5143114852</v>
+        <v>45072.30406106781</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>53.27350370793251</v>
@@ -31113,10 +31113,10 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>569858.6512436254</v>
+        <v>41613.59707669582</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>41.27669682992372</v>
+        <v>41.27669682992371</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -31153,10 +31153,10 @@
         <v>193.8046836844156</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>3230.919246817511</v>
+        <v>3230.91924681751</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>1376.52034078133</v>
+        <v>1376.520340781329</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>474.1870466229238</v>
@@ -31183,21 +31183,21 @@
         <v>208.2943256733983</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>2125.808464910487</v>
+        <v>2125.808464910488</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>VAGINAL ESTROGENS</t>
+          <t>RAPID ACTING</t>
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>461483.9312696232</v>
+        <v>35406.02786314076</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>159.5085771344216</v>
+        <v>247.3975859697775</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -31234,13 +31234,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>35422.05789572736</v>
+        <v>35422.05789572737</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>13995.20182096432</v>
+        <v>13995.20182096431</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -31249,13 +31249,13 @@
         <v>1900.058258153955</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>37084.87478692562</v>
+        <v>37084.87478692561</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>21605.89140012008</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>15097.20885202127</v>
+        <v>15097.20885202126</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>143.8256323506509</v>
@@ -31264,21 +31264,21 @@
         <v>1997.87208359685</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>38846.50756897045</v>
+        <v>38846.50756897044</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
       </c>
       <c r="AF68" s="82" t="inlineStr">
         <is>
-          <t>RAPID ACTING</t>
+          <t>VAGINAL ESTROGENS</t>
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>400146.5577244778</v>
+        <v>33594.02408892744</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>247.3975859697775</v>
+        <v>159.5085771344216</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -31432,7 +31432,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.75051817676518</v>
+        <v>7.750518176765183</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -31700,7 +31700,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755256</v>
+        <v>7197.985321755258</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -31715,13 +31715,13 @@
         <v>9732.017604071891</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8157.149229625106</v>
+        <v>8157.14922962511</v>
       </c>
       <c r="Q75" s="131" t="n">
         <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.95867935544807</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -31730,7 +31730,7 @@
         <v>11147.09612701664</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9996.096520677065</v>
+        <v>9996.096520677067</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3404.183159089577</v>
@@ -31858,10 +31858,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>232.6051624475786</v>
+        <v>232.6051624475787</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>232.6051624475786</v>
+        <v>232.6051624475787</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -31968,10 +31968,10 @@
         <v>4438</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2209.56854990732</v>
+        <v>2209.568549907321</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>2593.333683184456</v>
+        <v>2593.333683184457</v>
       </c>
       <c r="L79" s="131" t="n">
         <v>10.83583126299182</v>
@@ -31980,7 +31980,7 @@
         <v>26.18930320257346</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>4839.927367557341</v>
+        <v>4839.927367557343</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2292.902614467378</v>
@@ -31998,7 +31998,7 @@
         <v>4995.003831312751</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2339.927961197536</v>
+        <v>2339.927961197535</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2717.102643076893</v>
@@ -32679,7 +32679,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>2912.438830875361</v>
+        <v>2912.43883087536</v>
       </c>
     </row>
     <row r="90">
@@ -32774,7 +32774,7 @@
         <v>9604.744793221946</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>7.468734608523377</v>
+        <v>7.468734608523375</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>0</v>
@@ -32786,10 +32786,10 @@
         <v>9612.213527830469</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>9711.100612668351</v>
+        <v>9711.100612668355</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -32798,10 +32798,10 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>9718.782032960185</v>
+        <v>9718.782032960189</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473897</v>
+        <v>9788.465905473899</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>7.841870691875751</v>
@@ -32813,7 +32813,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165773</v>
+        <v>9796.307776165775</v>
       </c>
     </row>
     <row r="92">
@@ -32905,7 +32905,7 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173873</v>
+        <v>8942.039540173875</v>
       </c>
       <c r="K93" s="131" t="n">
         <v>3500.537314860515</v>
@@ -32920,13 +32920,13 @@
         <v>12582.48366843823</v>
       </c>
       <c r="P93" s="130" t="n">
-        <v>9792.362202164184</v>
+        <v>9792.362202164188</v>
       </c>
       <c r="Q93" s="131" t="n">
         <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888918</v>
       </c>
       <c r="S93" s="131" t="n">
         <v>62.2499783240786</v>
@@ -32938,7 +32938,7 @@
         <v>11405.71069303371</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4368.403547057688</v>
+        <v>4368.403547057689</v>
       </c>
       <c r="X93" s="131" t="n">
         <v>106.4689901288691</v>
@@ -33078,10 +33078,10 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1698.361346924145</v>
+        <v>1698.361346924144</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>1698.361346924145</v>
+        <v>1698.361346924144</v>
       </c>
     </row>
     <row r="96">
@@ -33176,10 +33176,10 @@
         <v>5685.3390405849</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>4472.570348548972</v>
+        <v>4472.570348548973</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>51.71639126361766</v>
+        <v>51.71639126361767</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>109.2666359584576</v>
@@ -33188,7 +33188,7 @@
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778224</v>
+        <v>6423.034571778222</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
@@ -33197,13 +33197,13 @@
         <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>118.6178170830754</v>
+        <v>118.6178170830753</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>11942.47622573674</v>
+        <v>11942.47622573673</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6613.078984960888</v>
+        <v>6613.078984960886</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>5523.444075919049</v>
@@ -33337,7 +33337,7 @@
         <v>11470.90211011721</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>3333.582500652556</v>
+        <v>3333.582500652527</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>9331.146765395853</v>
@@ -33346,10 +33346,10 @@
         <v>48.29562868547146</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>251.2530014457657</v>
+        <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>12964.27789617965</v>
+        <v>12964.27789617962</v>
       </c>
     </row>
     <row r="100">
@@ -33588,7 +33588,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.2085919510268</v>
+        <v>522.208591951027</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -33685,7 +33685,7 @@
         <v>3845.468296768772</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>2747.025908881709</v>
+        <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>511291.1640661132</v>
